--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487450_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487450_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6601</v>
+        <v>0.1962</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1695</v>
+        <v>-0.767</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8296</v>
+        <v>0.9631999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>0.09420000000000001</v>
@@ -610,13 +610,13 @@
         <v>1.5668</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5867</v>
+        <v>0.1228</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7111</v>
+        <v>0.1135</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1244</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>-0.6083</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.2295</v>
+        <v>-0.2027</v>
       </c>
       <c r="E3" t="n">
         <v>0.0204</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2499</v>
+        <v>-0.2232</v>
       </c>
       <c r="G3" t="n">
         <v>-0.2473</v>
@@ -688,13 +688,13 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. LOPE REBOLLO</t>
+          <t>S. MUJICA LANDAETA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.7342</v>
+        <v>-2.5313</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9006</v>
+        <v>1.4917</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.6348</v>
+        <v>-4.023</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.1275</v>
+        <v>-1.3963</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.769</v>
+        <v>-2.5131</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3585</v>
+        <v>1.1168</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3213</v>
+        <v>1.9899</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1548</v>
+        <v>0.6158</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1665</v>
+        <v>1.3741</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.4488</v>
+        <v>-3.3862</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.9237</v>
+        <v>-3.1289</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.525</v>
+        <v>-0.2573</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7834</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7626</v>
+        <v>0.5875</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6099</v>
+        <v>0.1404</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5585</v>
+        <v>0.4811</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.9487</v>
+        <v>-0.3407</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.8837</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.8837</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. MUJICA LANDAETA</t>
+          <t>S. LOPE REBOLLO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.251</v>
+        <v>-2.9028</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7988</v>
+        <v>-0.2681</v>
       </c>
       <c r="F5" t="n">
-        <v>-4.0498</v>
+        <v>-2.6348</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.3963</v>
+        <v>-3.1275</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.5131</v>
+        <v>-2.769</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1168</v>
+        <v>-0.3585</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9899</v>
+        <v>0.3213</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6158</v>
+        <v>0.1548</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3741</v>
+        <v>0.1665</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.3862</v>
+        <v>-3.4488</v>
       </c>
       <c r="N5" t="n">
-        <v>-3.1289</v>
+        <v>-2.9237</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2573</v>
+        <v>-0.525</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3917</v>
+        <v>0.7834</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5875</v>
+        <v>1.7626</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4207</v>
+        <v>-0.5587</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7881</v>
+        <v>0.3899</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3674</v>
+        <v>-0.9487</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.8837</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.8837</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-3.2121</v>
+        <v>-3.1085</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5336</v>
+        <v>-0.2695</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.6785</v>
+        <v>-2.8389</v>
       </c>
       <c r="G6" t="n">
         <v>0.1107</v>
@@ -922,13 +922,13 @@
         <v>0.9792</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2434</v>
+        <v>-0.1397</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.517</v>
+        <v>-0.2529</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2736</v>
+        <v>0.1132</v>
       </c>
       <c r="V6" t="n">
         <v>-2.1003</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.5028</v>
+        <v>-3.2387</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.7427</v>
+        <v>-1.4786</v>
       </c>
       <c r="F7" t="n">
         <v>-1.7601</v>
@@ -1000,10 +1000,10 @@
         <v>0.5875</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1575</v>
+        <v>-0.8934</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6952</v>
+        <v>-0.4311</v>
       </c>
       <c r="U7" t="n">
         <v>-0.4623</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.6248</v>
+        <v>-3.8874</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1988</v>
+        <v>0.4317</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.426</v>
+        <v>-4.3191</v>
       </c>
       <c r="G8" t="n">
         <v>-1.2962</v>
@@ -1078,13 +1078,13 @@
         <v>1.3709</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6592</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6775</v>
+        <v>-0.0471</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0184</v>
+        <v>0.1253</v>
       </c>
       <c r="V8" t="n">
         <v>-4.0403</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.1487</v>
+        <v>-4.6518</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4571</v>
+        <v>-0.8266</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.6916</v>
+        <v>-3.8253</v>
       </c>
       <c r="G9" t="n">
         <v>-3.7239</v>
@@ -1156,13 +1156,13 @@
         <v>2.1543</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6414</v>
+        <v>-0.1445</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5476</v>
+        <v>0.0829</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-0.2275</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. IGLESIAS CAMINO</t>
+          <t>C. GIL REY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.5828</v>
+        <v>-5.0191</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9451</v>
+        <v>-1.5438</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.6376</v>
+        <v>-3.4752</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.1527</v>
+        <v>-3.14</v>
       </c>
       <c r="H10" t="n">
-        <v>-5.8245</v>
+        <v>-2.9127</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6718</v>
+        <v>-0.2273</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.6383</v>
+        <v>1.5233</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.2186</v>
+        <v>0.8266</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5803</v>
+        <v>0.6967</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.5144</v>
+        <v>-4.6633</v>
       </c>
       <c r="N10" t="n">
-        <v>-3.606</v>
+        <v>-3.7393</v>
       </c>
       <c r="O10" t="n">
-        <v>1.0916</v>
+        <v>-0.924</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9792</v>
+        <v>-1.1751</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9792</v>
+        <v>-2.9377</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9585</v>
+        <v>1.7626</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3091</v>
+        <v>-0.704</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3276</v>
+        <v>-0.1294</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0185</v>
+        <v>-0.5746</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.1003</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C. GIL REY</t>
+          <t>A. IGLESIAS CAMINO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.482</v>
+        <v>-5.2906</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.686</v>
+        <v>-2.5193</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.796</v>
+        <v>-2.7713</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.14</v>
+        <v>-4.1527</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.9127</v>
+        <v>-5.8245</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2273</v>
+        <v>1.6718</v>
       </c>
       <c r="J11" t="n">
-        <v>1.5233</v>
+        <v>-1.6383</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8266</v>
+        <v>-2.2186</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6967</v>
+        <v>0.5803</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.6633</v>
+        <v>-2.5144</v>
       </c>
       <c r="N11" t="n">
-        <v>-3.7393</v>
+        <v>-3.606</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.924</v>
+        <v>1.0916</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.1751</v>
+        <v>0.9792</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.9377</v>
+        <v>-0.9792</v>
       </c>
       <c r="R11" t="n">
-        <v>1.7626</v>
+        <v>1.9585</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.1669</v>
+        <v>-0.0169</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.2716</v>
+        <v>0.0982</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8954</v>
+        <v>-0.1151</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-2.1003</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-2.1003</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.5472</v>
+        <v>-7.1272</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.3234</v>
+        <v>-1.7162</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.2239</v>
+        <v>-5.411</v>
       </c>
       <c r="G12" t="n">
         <v>-4.7278</v>
@@ -1390,13 +1390,13 @@
         <v>0.9792</v>
       </c>
       <c r="S12" t="n">
-        <v>1.2221</v>
+        <v>0.6421</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7287</v>
+        <v>0.3358</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4934</v>
+        <v>0.3063</v>
       </c>
       <c r="V12" t="n">
         <v>-3.0415</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-38.655</v>
+        <v>-37.7639</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.336399999999999</v>
+        <v>-7.4453</v>
       </c>
       <c r="F13" t="n">
-        <v>-30.3186</v>
+        <v>-30.3187</v>
       </c>
       <c r="G13" t="n">
         <v>-23.5604</v>
@@ -1468,13 +1468,13 @@
         <v>13.7091</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.3203</v>
+        <v>-1.4291</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2501</v>
+        <v>0.6409000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.0703</v>
+        <v>-2.0702</v>
       </c>
       <c r="V13" t="n">
         <v>-12.7744</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>12.8281</v>
+        <v>13.1636</v>
       </c>
       <c r="E14" t="n">
-        <v>12.0169</v>
+        <v>11.8123</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8111</v>
+        <v>1.3513</v>
       </c>
       <c r="G14" t="n">
         <v>7.096</v>
@@ -1546,13 +1546,13 @@
         <v>2.1543</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3564</v>
+        <v>0.6919</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6516</v>
+        <v>0.447</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2952</v>
+        <v>0.245</v>
       </c>
       <c r="V14" t="n">
         <v>4.2005</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>10.7343</v>
+        <v>8.399100000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>7.4941</v>
+        <v>5.4473</v>
       </c>
       <c r="F15" t="n">
-        <v>3.2402</v>
+        <v>2.9518</v>
       </c>
       <c r="G15" t="n">
         <v>5.9982</v>
@@ -1624,13 +1624,13 @@
         <v>2.546</v>
       </c>
       <c r="S15" t="n">
-        <v>4.0068</v>
+        <v>1.6716</v>
       </c>
       <c r="T15" t="n">
-        <v>3.143</v>
+        <v>1.0963</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8638</v>
+        <v>0.5754</v>
       </c>
       <c r="V15" t="n">
         <v>2.1003</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. GONZALEZ MOTA</t>
+          <t>L. MC-CARTHY SANTOS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.0458</v>
+        <v>6.6181</v>
       </c>
       <c r="E16" t="n">
-        <v>5.1133</v>
+        <v>4.7213</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9326</v>
+        <v>1.8967</v>
       </c>
       <c r="G16" t="n">
-        <v>7.0886</v>
+        <v>4.6108</v>
       </c>
       <c r="H16" t="n">
-        <v>5.7698</v>
+        <v>4.2515</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3189</v>
+        <v>0.3593</v>
       </c>
       <c r="J16" t="n">
-        <v>6.9241</v>
+        <v>4.5828</v>
       </c>
       <c r="K16" t="n">
-        <v>5.626</v>
+        <v>4.3807</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2981</v>
+        <v>0.2021</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1645</v>
+        <v>0.028</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1437</v>
+        <v>-0.1292</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0208</v>
+        <v>0.1572</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.1751</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9585</v>
+        <v>2.1543</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1591</v>
+        <v>-0.1091</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1476</v>
+        <v>-0.0988</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3068</v>
+        <v>-0.0103</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.8837</v>
+        <v>0.9412</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.8837</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. MC-CARTHY SANTOS</t>
+          <t>S. GONZALEZ MOTA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.5708</v>
+        <v>6.2311</v>
       </c>
       <c r="E17" t="n">
-        <v>4.1073</v>
+        <v>5.2156</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4635</v>
+        <v>1.0155</v>
       </c>
       <c r="G17" t="n">
-        <v>4.6108</v>
+        <v>7.0886</v>
       </c>
       <c r="H17" t="n">
-        <v>4.2515</v>
+        <v>5.7698</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3593</v>
+        <v>1.3189</v>
       </c>
       <c r="J17" t="n">
-        <v>4.5828</v>
+        <v>6.9241</v>
       </c>
       <c r="K17" t="n">
-        <v>4.3807</v>
+        <v>5.626</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2021</v>
+        <v>1.2981</v>
       </c>
       <c r="M17" t="n">
-        <v>0.028</v>
+        <v>0.1645</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1292</v>
+        <v>0.1437</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1572</v>
+        <v>0.0208</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1751</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1543</v>
+        <v>1.9585</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1564</v>
+        <v>0.0262</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7128</v>
+        <v>0.25</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4436</v>
+        <v>-0.2238</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9412</v>
+        <v>-0.8837</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2754</v>
+        <v>-0.8837</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.7436</v>
+        <v>5.0949</v>
       </c>
       <c r="E18" t="n">
-        <v>3.5872</v>
+        <v>4.0989</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1563</v>
+        <v>0.996</v>
       </c>
       <c r="G18" t="n">
         <v>0.8941</v>
@@ -1858,13 +1858,13 @@
         <v>1.3709</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1789</v>
+        <v>0.5302</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5346</v>
+        <v>-0.0229</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7135</v>
+        <v>0.5531</v>
       </c>
       <c r="V18" t="n">
         <v>4.2581</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.9188</v>
+        <v>2.6158</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6943</v>
+        <v>1.3083</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2245</v>
+        <v>1.3075</v>
       </c>
       <c r="G19" t="n">
         <v>0.1135</v>
@@ -1936,13 +1936,13 @@
         <v>1.9585</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6279</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4752</v>
+        <v>0.1388</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1527</v>
+        <v>-0.0697</v>
       </c>
       <c r="V19" t="n">
         <v>2.4332</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.4024</v>
+        <v>1.1489</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9034</v>
+        <v>0.5964</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4991</v>
+        <v>0.5525</v>
       </c>
       <c r="G20" t="n">
         <v>0.0723</v>
@@ -2014,13 +2014,13 @@
         <v>0.5875</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4097</v>
+        <v>0.1562</v>
       </c>
       <c r="T20" t="n">
-        <v>0.504</v>
+        <v>0.197</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.09429999999999999</v>
+        <v>-0.0409</v>
       </c>
       <c r="V20" t="n">
         <v>0.3329</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.645</v>
+        <v>0.0123</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0543</v>
+        <v>0.2527</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5908</v>
+        <v>-0.2405</v>
       </c>
       <c r="G21" t="n">
         <v>-0.2771</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3679</v>
+        <v>0.2894</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2376</v>
+        <v>0.0694</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1303</v>
+        <v>0.22</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3799</v>
+        <v>-0.9364</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7383999999999999</v>
+        <v>-0.4314</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6415</v>
+        <v>-0.5051</v>
       </c>
       <c r="G22" t="n">
         <v>-1.3622</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0176</v>
+        <v>0.4258</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1782</v>
+        <v>0.1288</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1606</v>
+        <v>0.297</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.5638</v>
+        <v>-2.3279</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.8052</v>
+        <v>-2.7029</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2414</v>
+        <v>0.375</v>
       </c>
       <c r="G23" t="n">
         <v>-0.6737</v>
@@ -2248,13 +2248,13 @@
         <v>0.9792</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3026</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2376</v>
+        <v>-0.1353</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.065</v>
+        <v>0.0687</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6083</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>38.6551</v>
+        <v>40.0195</v>
       </c>
       <c r="E24" t="n">
-        <v>30.3186</v>
+        <v>30.3185</v>
       </c>
       <c r="F24" t="n">
-        <v>8.336399999999999</v>
+        <v>9.700699999999999</v>
       </c>
       <c r="G24" t="n">
         <v>23.5605</v>
@@ -2326,13 +2326,13 @@
         <v>13.7092</v>
       </c>
       <c r="S24" t="n">
-        <v>2.3203</v>
+        <v>3.6847</v>
       </c>
       <c r="T24" t="n">
-        <v>2.0702</v>
+        <v>2.0703</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2499999999999999</v>
+        <v>1.6145</v>
       </c>
       <c r="V24" t="n">
         <v>12.7742</v>
